--- a/docs/Mapping_casi_uso/cittadinanza/Citt_043.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_043.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="141">
   <si>
     <t>Sezione</t>
   </si>
@@ -149,7 +149,16 @@
     <t>estremiDecretoConferimento</t>
   </si>
   <si>
-    <t>Sindaco</t>
+    <t xml:space="preserve">Officiante </t>
+  </si>
+  <si>
+    <t>Ufficiale di stato civile delegato al giuramento di cittadinanza</t>
+  </si>
+  <si>
+    <t>officiante</t>
+  </si>
+  <si>
+    <t>opzionale</t>
   </si>
   <si>
     <t>Cognome</t>
@@ -159,9 +168,6 @@
   </si>
   <si>
     <t>cognome</t>
-  </si>
-  <si>
-    <t>opzionale</t>
   </si>
   <si>
     <t>Nome</t>
@@ -487,11 +493,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.75390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.37109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="55.49609375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="28.6484375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="27.421875" customWidth="true" bestFit="true"/>
@@ -993,16 +999,16 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -1010,13 +1016,13 @@
         <v>45</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>51</v>
@@ -1025,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
@@ -1036,10 +1042,10 @@
         <v>52</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>53</v>
@@ -1048,7 +1054,7 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -1062,7 +1068,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>55</v>
@@ -1071,7 +1077,7 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
@@ -1085,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>57</v>
@@ -1094,7 +1100,7 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
@@ -1108,7 +1114,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>59</v>
@@ -1117,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28">
@@ -1131,7 +1137,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>61</v>
@@ -1140,7 +1146,7 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
@@ -1154,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>63</v>
@@ -1163,7 +1169,7 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
@@ -1177,7 +1183,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>65</v>
@@ -1186,7 +1192,7 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
@@ -1200,7 +1206,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>67</v>
@@ -1209,7 +1215,7 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32">
@@ -1223,7 +1229,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>69</v>
@@ -1232,7 +1238,7 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33">
@@ -1246,7 +1252,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>71</v>
@@ -1255,7 +1261,7 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34">
@@ -1269,7 +1275,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>73</v>
@@ -1278,7 +1284,7 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35">
@@ -1292,7 +1298,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>75</v>
@@ -1301,7 +1307,7 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36">
@@ -1315,7 +1321,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>77</v>
@@ -1324,7 +1330,7 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37">
@@ -1338,7 +1344,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>79</v>
@@ -1347,7 +1353,7 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38">
@@ -1361,7 +1367,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>81</v>
@@ -1370,7 +1376,7 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39">
@@ -1384,7 +1390,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>83</v>
@@ -1393,7 +1399,7 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40">
@@ -1407,7 +1413,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>85</v>
@@ -1416,7 +1422,7 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41">
@@ -1430,7 +1436,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>87</v>
@@ -1439,7 +1445,7 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42">
@@ -1453,7 +1459,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>89</v>
@@ -1462,7 +1468,7 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43">
@@ -1476,7 +1482,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>91</v>
@@ -1485,7 +1491,7 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44">
@@ -1496,10 +1502,10 @@
         <v>92</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>93</v>
@@ -1508,7 +1514,7 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45">
@@ -1522,7 +1528,7 @@
         <v>12</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>95</v>
@@ -1531,7 +1537,7 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46">
@@ -1542,10 +1548,10 @@
         <v>96</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>97</v>
@@ -1554,50 +1560,50 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="C47" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="F47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>28</v>
@@ -1605,22 +1611,22 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>28</v>
@@ -1628,22 +1634,22 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>28</v>
@@ -1651,16 +1657,16 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>55</v>
@@ -1674,7 +1680,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>56</v>
@@ -1683,7 +1689,7 @@
         <v>12</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>57</v>
@@ -1697,16 +1703,16 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>59</v>
@@ -1720,16 +1726,16 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>61</v>
@@ -1743,16 +1749,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>63</v>
@@ -1766,22 +1772,22 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>65</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>28</v>
@@ -1789,22 +1795,22 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>67</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>28</v>
@@ -1812,22 +1818,22 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>28</v>
@@ -1835,16 +1841,16 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>71</v>
@@ -1858,22 +1864,22 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>28</v>
@@ -1881,16 +1887,16 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>75</v>
@@ -1904,22 +1910,22 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>77</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>28</v>
@@ -1927,22 +1933,22 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>28</v>
@@ -1950,22 +1956,22 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>81</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>28</v>
@@ -1973,22 +1979,22 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>28</v>
@@ -1996,22 +2002,22 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>28</v>
@@ -2019,22 +2025,22 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>87</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>28</v>
@@ -2042,22 +2048,22 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>28</v>
@@ -2065,16 +2071,16 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>91</v>
@@ -2088,22 +2094,22 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>28</v>
@@ -2111,7 +2117,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>118</v>
@@ -2120,13 +2126,13 @@
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>119</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>28</v>
@@ -2134,7 +2140,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>120</v>
@@ -2143,13 +2149,13 @@
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>121</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>28</v>
@@ -2157,7 +2163,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>122</v>
@@ -2166,13 +2172,13 @@
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>123</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>28</v>
@@ -2180,22 +2186,22 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>28</v>
@@ -2203,7 +2209,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>94</v>
@@ -2212,7 +2218,7 @@
         <v>12</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>95</v>
@@ -2226,16 +2232,16 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>97</v>
@@ -2249,62 +2255,62 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>53</v>
@@ -2313,21 +2319,21 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>55</v>
@@ -2336,12 +2342,12 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>56</v>
@@ -2350,7 +2356,7 @@
         <v>12</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>57</v>
@@ -2359,12 +2365,12 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>58</v>
@@ -2373,7 +2379,7 @@
         <v>12</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>59</v>
@@ -2382,12 +2388,12 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>60</v>
@@ -2396,7 +2402,7 @@
         <v>12</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>61</v>
@@ -2405,21 +2411,21 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>63</v>
@@ -2428,12 +2434,12 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>64</v>
@@ -2442,21 +2448,21 @@
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>65</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>66</v>
@@ -2465,21 +2471,21 @@
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>67</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>68</v>
@@ -2488,21 +2494,21 @@
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>70</v>
@@ -2511,44 +2517,44 @@
         <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>71</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>74</v>
@@ -2557,7 +2563,7 @@
         <v>12</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>75</v>
@@ -2566,58 +2572,58 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E91" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>78</v>
@@ -2626,21 +2632,21 @@
         <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>80</v>
@@ -2649,21 +2655,21 @@
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>81</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>82</v>
@@ -2672,21 +2678,21 @@
         <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>84</v>
@@ -2695,21 +2701,21 @@
         <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>86</v>
@@ -2718,21 +2724,21 @@
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>87</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>88</v>
@@ -2741,21 +2747,21 @@
         <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>90</v>
@@ -2764,44 +2770,44 @@
         <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>91</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>93</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>94</v>
@@ -2810,7 +2816,7 @@
         <v>12</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>95</v>
@@ -2819,12 +2825,12 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>96</v>
@@ -2833,7 +2839,7 @@
         <v>12</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>97</v>
@@ -2842,50 +2848,50 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>136</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>28</v>
@@ -2893,24 +2899,47 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>138</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G105" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" s="2" t="s">
         <v>28</v>
       </c>
     </row>
